--- a/figs/data/mixU_v4.xlsx
+++ b/figs/data/mixU_v4.xlsx
@@ -455,350 +455,6 @@
           </yVal>
           <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="8"/>
-          <order val="8"/>
-          <tx>
-            <strRef>
-              <f>'WAF 추이'!S1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'WAF 추이'!$R$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'WAF 추이'!$S$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="9"/>
-          <order val="9"/>
-          <tx>
-            <strRef>
-              <f>'WAF 추이'!U1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'WAF 추이'!$T$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'WAF 추이'!$U$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="10"/>
-          <order val="10"/>
-          <tx>
-            <strRef>
-              <f>'WAF 추이'!W1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'WAF 추이'!$V$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'WAF 추이'!$W$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="11"/>
-          <order val="11"/>
-          <tx>
-            <strRef>
-              <f>'WAF 추이'!Y1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'WAF 추이'!$X$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'WAF 추이'!$Y$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="12"/>
-          <order val="12"/>
-          <tx>
-            <strRef>
-              <f>'WAF 추이'!AA1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'WAF 추이'!$Z$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'WAF 추이'!$AA$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="13"/>
-          <order val="13"/>
-          <tx>
-            <strRef>
-              <f>'WAF 추이'!AC1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'WAF 추이'!$AB$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'WAF 추이'!$AC$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="14"/>
-          <order val="14"/>
-          <tx>
-            <strRef>
-              <f>'WAF 추이'!AE1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'WAF 추이'!$AD$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'WAF 추이'!$AE$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="15"/>
-          <order val="15"/>
-          <tx>
-            <strRef>
-              <f>'WAF 추이'!AG1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'WAF 추이'!$AF$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'WAF 추이'!$AG$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -863,66 +519,6 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
-      <legendEntry>
-        <idx val="1"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="2"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="3"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="4"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="5"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="6"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="7"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="8"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="9"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="10"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="11"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="12"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="13"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="14"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="15"/>
-        <delete val="1"/>
-      </legendEntry>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1203,135 +799,6 @@
           </yVal>
           <smooth val="0"/>
         </ser>
-        <ser>
-          <idx val="4"/>
-          <order val="4"/>
-          <tx>
-            <strRef>
-              <f>'학습 (후보 수)'!K1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$J$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$K$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="5"/>
-          <order val="5"/>
-          <tx>
-            <strRef>
-              <f>'학습 (후보 수)'!M1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$L$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$M$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="6"/>
-          <order val="6"/>
-          <tx>
-            <strRef>
-              <f>'학습 (후보 수)'!O1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showSerName val="1"/>
-          </dLbls>
-          <xVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$N$2</f>
-            </numRef>
-          </xVal>
-          <yVal>
-            <numRef>
-              <f>'학습 (후보 수)'!$O$2</f>
-            </numRef>
-          </yVal>
-          <smooth val="0"/>
-        </ser>
         <axId val="10"/>
         <axId val="20"/>
       </scatterChart>
@@ -1396,26 +863,6 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
-      <legendEntry>
-        <idx val="2"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="3"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="4"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="5"/>
-        <delete val="1"/>
-      </legendEntry>
-      <legendEntry>
-        <idx val="6"/>
-        <delete val="1"/>
-      </legendEntry>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1427,7 +874,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>34</col>
+      <col>18</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1481,7 +928,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>16</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1793,7 +1240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1809,152 +1256,72 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>선1 x</t>
+          <t>→ 2.Varmail WAF 2.42 x</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>선1</t>
+          <t>→ 2.Varmail WAF 2.42</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>선2 x</t>
+          <t>→ 3.FIO-Fast WAF 5.21 x</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>선2</t>
+          <t>→ 3.FIO-Fast WAF 5.21</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>선3 x</t>
+          <t>→ 4.Varmail WAF 2.54 x</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>선3</t>
+          <t>→ 4.Varmail WAF 2.54</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>선4 x</t>
+          <t>→ 5.FIO-Fast WAF 5.01 x</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>선4</t>
+          <t>→ 5.FIO-Fast WAF 5.01</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>선5 x</t>
+          <t>→ 6.Varmail WAF 2.61 x</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>선5</t>
+          <t>→ 6.Varmail WAF 2.61</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>선6 x</t>
+          <t>→ 7.FIO-Fast WAF 5.14 x</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>선6</t>
+          <t>→ 7.FIO-Fast WAF 5.14</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>선7 x</t>
+          <t>→ 8.Varmail WAF 2.57 x</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>선7</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>라벨1 x</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>1.FIO-Fast WAF 1.86</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>라벨2 x</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>2.Varmail WAF 2.42</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>라벨3 x</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>3.FIO-Fast WAF 5.21</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>라벨4 x</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>4.Varmail WAF 2.54</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>라벨5 x</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>5.FIO-Fast WAF 5.01</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>라벨6 x</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>6.Varmail WAF 2.61</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>라벨7 x</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>7.FIO-Fast WAF 5.14</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>라벨8 x</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>8.Varmail WAF 2.57</t>
+          <t>→ 8.Varmail WAF 2.57</t>
         </is>
       </c>
     </row>
@@ -2007,54 +1374,6 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.873</v>
-      </c>
-      <c r="U2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3.124</v>
-      </c>
-      <c r="W2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.375</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5.625</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>6.876</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8.125999999999999</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>9.372999999999999</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>5.7</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2321,7 +1640,7 @@
       <c r="B30" t="n">
         <v>2.4589</v>
       </c>
-      <c r="AI30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>점선 = 워크로드 전환, 위 글자 = 구간 이름과 그 구간 평균 WAF. iCAT-v4 1회(두 번째 PC). 구간 8개 × 4500초. 고정 CAT(기본·견고·최적)은 아직 이 혼합으로 측정하지 않음.</t>
         </is>
@@ -2585,7 +1904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X293"/>
+  <dimension ref="A1:R293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2611,52 +1930,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>선1 x</t>
+          <t>→ 2회차 Varmail+FIO-Fast x</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>선1</t>
+          <t>→ 2회차 Varmail+FIO-Fast</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>선2 x</t>
+          <t>→ 3회차 Varmail+FIO-Fast+Varmail+FIO-Fast+Varmail x</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>선2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>라벨1 x</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>1회차 FIO-Fast</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>라벨2 x</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>2회차 Varmail+FIO-Fast</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>라벨3 x</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>3회차 Varmail+FIO-Fast+Varmail+FIO-Fast+Varmail</t>
+          <t>→ 3회차 Varmail+FIO-Fast+Varmail+FIO-Fast+Varmail</t>
         </is>
       </c>
     </row>
@@ -2685,24 +1974,6 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>48</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>48</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>48</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3135,42 +2406,42 @@
       <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="Q32" s="1" t="inlineStr">
+      <c r="K32" s="1" t="inlineStr">
         <is>
           <t>회차</t>
         </is>
       </c>
-      <c r="R32" s="1" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>워크로드</t>
         </is>
       </c>
-      <c r="S32" s="1" t="inlineStr">
+      <c r="M32" s="1" t="inlineStr">
         <is>
           <t>시작(h)</t>
         </is>
       </c>
-      <c r="T32" s="1" t="inlineStr">
+      <c r="N32" s="1" t="inlineStr">
         <is>
           <t>끝(h)</t>
         </is>
       </c>
-      <c r="U32" s="1" t="inlineStr">
+      <c r="O32" s="1" t="inlineStr">
         <is>
           <t>시험 횟수</t>
         </is>
       </c>
-      <c r="V32" s="1" t="inlineStr">
+      <c r="P32" s="1" t="inlineStr">
         <is>
           <t>처음 후보</t>
         </is>
       </c>
-      <c r="W32" s="1" t="inlineStr">
+      <c r="Q32" s="1" t="inlineStr">
         <is>
           <t>최소 후보</t>
         </is>
       </c>
-      <c r="X32" s="1" t="inlineStr">
+      <c r="R32" s="1" t="inlineStr">
         <is>
           <t>마지막 최고 후보</t>
         </is>
@@ -3189,30 +2460,30 @@
       <c r="D33" t="n">
         <v>6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>1.FIO-Fast</t>
         </is>
       </c>
-      <c r="S33" t="n">
+      <c r="M33" t="n">
         <v>0</v>
       </c>
-      <c r="T33" t="n">
+      <c r="N33" t="n">
         <v>1.32</v>
       </c>
-      <c r="U33" t="n">
+      <c r="O33" t="n">
         <v>323</v>
       </c>
-      <c r="V33" t="n">
+      <c r="P33" t="n">
         <v>45</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Q33" t="n">
         <v>11</v>
       </c>
-      <c r="X33" t="n">
+      <c r="R33" t="n">
         <v>46</v>
       </c>
     </row>
@@ -3229,30 +2500,30 @@
       <c r="D34" t="n">
         <v>5</v>
       </c>
-      <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" t="inlineStr">
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>2.Varmail+3.FIO-Fast</t>
         </is>
       </c>
-      <c r="S34" t="n">
+      <c r="M34" t="n">
         <v>1.32</v>
       </c>
-      <c r="T34" t="n">
+      <c r="N34" t="n">
         <v>3.76</v>
       </c>
-      <c r="U34" t="n">
+      <c r="O34" t="n">
         <v>1136</v>
       </c>
-      <c r="V34" t="n">
+      <c r="P34" t="n">
         <v>20</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Q34" t="n">
         <v>5</v>
       </c>
-      <c r="X34" t="n">
+      <c r="R34" t="n">
         <v>47</v>
       </c>
     </row>
@@ -3269,30 +2540,30 @@
       <c r="D35" t="n">
         <v>4</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3</v>
-      </c>
-      <c r="R35" t="inlineStr">
+      <c r="K35" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>4.Varmail+5.FIO-Fast+6.Varmail+7.FIO-Fast+8.Varmail</t>
         </is>
       </c>
-      <c r="S35" t="n">
+      <c r="M35" t="n">
         <v>3.76</v>
       </c>
-      <c r="T35" t="n">
+      <c r="N35" t="n">
         <v>10</v>
       </c>
-      <c r="U35" t="n">
+      <c r="O35" t="n">
         <v>3093</v>
       </c>
-      <c r="V35" t="n">
+      <c r="P35" t="n">
         <v>13</v>
       </c>
-      <c r="W35" t="n">
-        <v>3</v>
-      </c>
-      <c r="X35" t="n">
+      <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
         <v>47</v>
       </c>
     </row>

--- a/figs/data/mixU_v4.xlsx
+++ b/figs/data/mixU_v4.xlsx
@@ -694,9 +694,6 @@
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
               <a:noFill/>
-              <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
-              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
